--- a/data/trans_dic/P41D_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P41D_2023-Edad-trans_dic.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto a la última vez que lo intentaron se quedó embarazada</t>
+          <t>Población que con respecto a la última vez que lo intentaron se quedó embarazada (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -539,7 +539,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -577,19 +577,19 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,91; 80,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5,2; 65,97</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -622,24 +622,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>0,0; 82,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,6; 84,17</t>
+          <t>0,0; 59,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 60,46</t>
+          <t>0,0; 52,39</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -672,24 +672,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,33</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,31</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -722,238 +722,34 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>0,0; 43,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,28; 59,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>7,36; 41,91</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>9,82%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>30,93%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>19,63%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 45,62</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>8,55; 60,85</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>7,31; 41,09</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="5">
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -965,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -978,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que con respecto a la última vez que lo intentaron se quedó embarazada</t>
+          <t>Población que con respecto a la última vez que lo intentaron se quedó embarazada (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1027,7 +823,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1042,12 +838,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1060,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2847</t>
         </is>
       </c>
     </row>
@@ -1088,19 +884,19 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>721; 5344</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>569; 7225</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1110,17 +906,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1133,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>724</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2032</t>
         </is>
       </c>
     </row>
@@ -1156,24 +952,24 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2473</t>
+          <t>0; 4475</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>766; 5560</t>
+          <t>0; 2953</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>379; 6622</t>
+          <t>0; 5434</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1183,17 +979,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1229,24 +1025,24 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4529</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2979</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5426</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1256,17 +1052,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3571</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4879</t>
         </is>
       </c>
     </row>
@@ -1302,329 +1098,33 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1567</t>
+          <t>0; 5732</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1071; 6917</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1567</t>
+          <t>1830; 10417</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>55-64</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>1307</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>3571</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>4879</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>0; 6071</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>986; 7024</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>1816; 10213</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="5">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A25:A27"/>
-    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P41D_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P41D_2023-Edad-trans_dic.xlsx
@@ -554,12 +554,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,91; 80,9</t>
+          <t>11,66; 85,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,2; 65,97</t>
+          <t>0,0; 61,19</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,36</t>
+          <t>0,0; 81,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,79</t>
+          <t>0,0; 66,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,39</t>
+          <t>0,0; 56,99</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,08</t>
+          <t>0,0; 41,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,28; 59,91</t>
+          <t>8,52; 61,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 41,91</t>
+          <t>6,77; 40,57</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2844</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>721; 5344</t>
+          <t>799; 5870</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>569; 7225</t>
+          <t>0; 7204</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>787</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2049</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4475</t>
+          <t>0; 4512</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2953</t>
+          <t>0; 3351</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5434</t>
+          <t>0; 6008</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4893</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5732</t>
+          <t>0; 5855</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1071; 6917</t>
+          <t>1012; 7250</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1830; 10417</t>
+          <t>1765; 10568</t>
         </is>
       </c>
     </row>
